--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786EDD19-8D32-48EC-9A47-5DFB9015A1DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1823504-2F7F-4628-97B7-1525BB6B8FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="200">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -601,13 +601,34 @@
   </si>
   <si>
     <t>Công Ty CP Công Nghệ Điện Tử &amp; Viễn Thông Việt Nam</t>
+  </si>
+  <si>
+    <t>Module định vị vệ tinh GPS/GNSS</t>
+  </si>
+  <si>
+    <t>Module định vị GPS/GNSS (Skylab)</t>
+  </si>
+  <si>
+    <t>IC phân chuyển nguồn (Power Distribution Switch)</t>
+  </si>
+  <si>
+    <t>IC điều khiển nguồn xung Hạ áp (Synchronous Step-Down Controller)</t>
+  </si>
+  <si>
+    <t>Transistor trường (N-Channel MOSFET)</t>
+  </si>
+  <si>
+    <t>IC nguồn xung hạ áp (Buck Converter)</t>
+  </si>
+  <si>
+    <t>Module SIM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -739,6 +760,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1013,7 +1040,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1078,27 +1105,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1162,21 +1168,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1198,14 +1192,8 @@
     <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1241,6 +1229,48 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1619,8 +1649,8 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="72"/>
-      <c r="C1" s="79" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="66" t="s">
         <v>192</v>
       </c>
       <c r="D1" s="23"/>
@@ -1631,116 +1661,116 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="80" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="67" t="s">
         <v>173</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="75"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="83" t="s">
+      <c r="B3" s="60"/>
+      <c r="C3" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="76"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="81" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="68" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="76"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="63"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="82" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="78"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="78"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="80"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="82"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
       <c r="E9" s="13"/>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="38" t="s">
+      <c r="F10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="31" t="s">
         <v>179</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -1748,1906 +1778,1910 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="39">
-        <v>1</v>
-      </c>
-      <c r="B11" s="39" t="s">
+      <c r="A11" s="32">
+        <v>1</v>
+      </c>
+      <c r="B11" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="41">
-        <v>1</v>
-      </c>
-      <c r="G11" s="42">
+      <c r="E11" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="34">
+        <v>1</v>
+      </c>
+      <c r="G11" s="35">
         <v>12000</v>
       </c>
       <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="39">
+      <c r="A12" s="32">
         <v>2</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12" s="46">
-        <v>1</v>
-      </c>
-      <c r="G12" s="42">
+      <c r="E12" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="39">
+        <v>1</v>
+      </c>
+      <c r="G12" s="35">
         <v>31000</v>
       </c>
       <c r="H12" s="26"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="39">
+      <c r="A13" s="32">
         <v>3</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="46">
-        <v>1</v>
-      </c>
-      <c r="G13" s="42">
+      <c r="E13" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="39">
+        <v>1</v>
+      </c>
+      <c r="G13" s="35">
         <v>31000</v>
       </c>
       <c r="H13" s="26"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="39">
+      <c r="A14" s="32">
         <v>4</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="41">
-        <v>1</v>
-      </c>
-      <c r="G14" s="42">
+      <c r="E14" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="34">
+        <v>1</v>
+      </c>
+      <c r="G14" s="35">
         <v>38000</v>
       </c>
       <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="39">
+      <c r="A15" s="32">
         <v>5</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="46">
-        <v>1</v>
-      </c>
-      <c r="G15" s="42">
+      <c r="E15" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="39">
+        <v>1</v>
+      </c>
+      <c r="G15" s="35">
         <v>375000</v>
       </c>
       <c r="H15" s="22"/>
     </row>
     <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39">
+      <c r="A16" s="32">
         <v>6</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="41">
-        <v>1</v>
-      </c>
-      <c r="G16" s="42">
+      <c r="E16" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="34">
+        <v>1</v>
+      </c>
+      <c r="G16" s="35">
         <v>9000</v>
       </c>
       <c r="H16" s="19"/>
     </row>
     <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="39">
+      <c r="A17" s="32">
         <v>7</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="46">
-        <v>1</v>
-      </c>
-      <c r="G17" s="42">
+      <c r="E17" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="39">
+        <v>1</v>
+      </c>
+      <c r="G17" s="35">
         <v>88000</v>
       </c>
       <c r="H17" s="19"/>
     </row>
     <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39">
+      <c r="A18" s="32">
         <v>8</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F18" s="41">
-        <v>1</v>
-      </c>
-      <c r="G18" s="42">
+      <c r="E18" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="34">
+        <v>1</v>
+      </c>
+      <c r="G18" s="35">
         <v>63000</v>
       </c>
       <c r="H18" s="19"/>
     </row>
     <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39">
+      <c r="A19" s="32">
         <v>9</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="41">
-        <v>1</v>
-      </c>
-      <c r="G19" s="42">
+      <c r="E19" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="34">
+        <v>1</v>
+      </c>
+      <c r="G19" s="35">
         <v>320000</v>
       </c>
       <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39">
+      <c r="A20" s="32">
         <v>10</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" s="46">
-        <v>1</v>
-      </c>
-      <c r="G20" s="42">
+      <c r="E20" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="39">
+        <v>1</v>
+      </c>
+      <c r="G20" s="35">
         <v>450000</v>
       </c>
       <c r="H20" s="11"/>
     </row>
     <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="39">
+      <c r="A21" s="32">
         <v>11</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="41">
-        <v>1</v>
-      </c>
-      <c r="G21" s="42">
+      <c r="E21" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="34">
+        <v>1</v>
+      </c>
+      <c r="G21" s="35">
         <v>275000</v>
       </c>
       <c r="H21" s="11"/>
     </row>
     <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39">
+      <c r="A22" s="32">
         <v>12</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="46">
-        <v>1</v>
-      </c>
-      <c r="G22" s="42">
+      <c r="E22" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="39">
+        <v>1</v>
+      </c>
+      <c r="G22" s="35">
         <v>385000</v>
       </c>
       <c r="H22" s="11"/>
     </row>
     <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39">
+      <c r="A23" s="32">
         <v>13</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="41">
-        <v>1</v>
-      </c>
-      <c r="G23" s="42">
+      <c r="E23" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="34">
+        <v>1</v>
+      </c>
+      <c r="G23" s="35">
         <v>385000</v>
       </c>
       <c r="H23" s="11"/>
     </row>
     <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39">
+      <c r="A24" s="32">
         <v>14</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="46">
-        <v>1</v>
-      </c>
-      <c r="G24" s="42">
+      <c r="E24" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="39">
+        <v>1</v>
+      </c>
+      <c r="G24" s="35">
         <v>240000</v>
       </c>
       <c r="H24" s="9"/>
     </row>
     <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39">
+      <c r="A25" s="32">
         <v>15</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="46">
-        <v>1</v>
-      </c>
-      <c r="G25" s="42">
+      <c r="E25" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="39">
+        <v>1</v>
+      </c>
+      <c r="G25" s="35">
         <v>240000</v>
       </c>
       <c r="H25" s="11"/>
     </row>
     <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39">
+      <c r="A26" s="32">
         <v>16</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="41">
-        <v>1</v>
-      </c>
-      <c r="G26" s="42">
+      <c r="E26" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="34">
+        <v>1</v>
+      </c>
+      <c r="G26" s="35">
         <v>240000</v>
       </c>
       <c r="H26" s="11"/>
     </row>
     <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="39">
+      <c r="A27" s="32">
         <v>17</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E27" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="46">
-        <v>1</v>
-      </c>
-      <c r="G27" s="42">
+      <c r="E27" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="39">
+        <v>1</v>
+      </c>
+      <c r="G27" s="35">
         <v>240000</v>
       </c>
       <c r="H27" s="9"/>
     </row>
     <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="39">
+      <c r="A28" s="32">
         <v>18</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F28" s="41">
-        <v>1</v>
-      </c>
-      <c r="G28" s="42">
+      <c r="E28" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="34">
+        <v>1</v>
+      </c>
+      <c r="G28" s="35">
         <v>38000</v>
       </c>
       <c r="H28" s="9"/>
     </row>
     <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="39">
+      <c r="A29" s="32">
         <v>19</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="46">
-        <v>1</v>
-      </c>
-      <c r="G29" s="42">
+      <c r="E29" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="39">
+        <v>1</v>
+      </c>
+      <c r="G29" s="35">
         <v>38000</v>
       </c>
       <c r="H29" s="9"/>
     </row>
     <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="39">
+      <c r="A30" s="32">
         <v>20</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="D30" s="40" t="s">
+      <c r="D30" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="41">
-        <v>1</v>
-      </c>
-      <c r="G30" s="42">
+      <c r="E30" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="34">
+        <v>1</v>
+      </c>
+      <c r="G30" s="35">
         <v>38000</v>
       </c>
       <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="39">
+      <c r="A31" s="32">
         <v>21</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E31" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="46">
-        <v>1</v>
-      </c>
-      <c r="G31" s="42">
+      <c r="E31" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="39">
+        <v>1</v>
+      </c>
+      <c r="G31" s="35">
         <v>12000</v>
       </c>
       <c r="H31" s="9"/>
     </row>
     <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="39">
+      <c r="A32" s="32">
         <v>22</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="50" t="s">
+      <c r="D32" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" s="41">
-        <v>1</v>
-      </c>
-      <c r="G32" s="42">
+      <c r="E32" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="34">
+        <v>1</v>
+      </c>
+      <c r="G32" s="35">
         <v>138000</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="39">
+      <c r="A33" s="32">
         <v>23</v>
       </c>
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="50" t="s">
+      <c r="D33" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" s="41">
-        <v>1</v>
-      </c>
-      <c r="G33" s="42">
+      <c r="E33" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="34">
+        <v>1</v>
+      </c>
+      <c r="G33" s="35">
         <v>138000</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="39">
+      <c r="A34" s="32">
         <v>24</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="D34" s="50" t="s">
+      <c r="D34" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="E34" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="46">
-        <v>1</v>
-      </c>
-      <c r="G34" s="42">
+      <c r="E34" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="39">
+        <v>1</v>
+      </c>
+      <c r="G34" s="35">
         <v>138000</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="39">
+      <c r="A35" s="32">
         <v>25</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="D35" s="50" t="s">
+      <c r="D35" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="41">
-        <v>1</v>
-      </c>
-      <c r="G35" s="42">
+      <c r="E35" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="34">
+        <v>1</v>
+      </c>
+      <c r="G35" s="35">
         <v>150000</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="39">
+      <c r="A36" s="32">
         <v>26</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="50" t="s">
+      <c r="D36" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="E36" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F36" s="46">
-        <v>1</v>
-      </c>
-      <c r="G36" s="42">
+      <c r="E36" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" s="39">
+        <v>1</v>
+      </c>
+      <c r="G36" s="35">
         <v>150000</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="39">
+      <c r="A37" s="32">
         <v>27</v>
       </c>
-      <c r="B37" s="52" t="s">
+      <c r="B37" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F37" s="41">
-        <v>1</v>
-      </c>
-      <c r="G37" s="42">
+      <c r="E37" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="34">
+        <v>1</v>
+      </c>
+      <c r="G37" s="35">
         <v>50000</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="39">
+      <c r="A38" s="32">
         <v>28</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38" s="46">
-        <v>1</v>
-      </c>
-      <c r="G38" s="42">
+      <c r="E38" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="39">
+        <v>1</v>
+      </c>
+      <c r="G38" s="35">
         <v>38000</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="39">
+      <c r="A39" s="32">
         <v>29</v>
       </c>
-      <c r="B39" s="48" t="s">
+      <c r="B39" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="48" t="s">
+      <c r="C39" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F39" s="41">
-        <v>1</v>
-      </c>
-      <c r="G39" s="42">
+      <c r="E39" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="34">
+        <v>1</v>
+      </c>
+      <c r="G39" s="35">
         <v>6000</v>
       </c>
       <c r="H39" s="9"/>
     </row>
     <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="39">
+      <c r="A40" s="32">
         <v>30</v>
       </c>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="48" t="s">
+      <c r="C40" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F40" s="46">
-        <v>1</v>
-      </c>
-      <c r="G40" s="42">
+      <c r="E40" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="39">
+        <v>1</v>
+      </c>
+      <c r="G40" s="35">
         <v>6000</v>
       </c>
       <c r="H40" s="9"/>
     </row>
     <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="39">
+      <c r="A41" s="32">
         <v>31</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="48" t="s">
+      <c r="C41" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="40" t="s">
+      <c r="D41" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" s="41">
-        <v>1</v>
-      </c>
-      <c r="G41" s="42">
+      <c r="E41" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41" s="34">
+        <v>1</v>
+      </c>
+      <c r="G41" s="35">
         <v>6000</v>
       </c>
       <c r="H41" s="9"/>
     </row>
     <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="39">
+      <c r="A42" s="32">
         <v>32</v>
       </c>
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="48" t="s">
+      <c r="C42" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="40" t="s">
+      <c r="D42" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F42" s="46">
-        <v>1</v>
-      </c>
-      <c r="G42" s="42">
+      <c r="E42" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42" s="39">
+        <v>1</v>
+      </c>
+      <c r="G42" s="35">
         <v>6000</v>
       </c>
       <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="39">
+      <c r="A43" s="32">
         <v>33</v>
       </c>
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="C43" s="47" t="s">
+      <c r="C43" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="D43" s="40" t="s">
+      <c r="D43" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F43" s="41">
-        <v>1</v>
-      </c>
-      <c r="G43" s="42">
+      <c r="E43" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F43" s="34">
+        <v>1</v>
+      </c>
+      <c r="G43" s="35">
         <v>12000</v>
       </c>
       <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="39">
+      <c r="A44" s="32">
         <v>34</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="48" t="s">
+      <c r="C44" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="40" t="s">
+      <c r="D44" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="46">
-        <v>1</v>
-      </c>
-      <c r="G44" s="42">
+      <c r="E44" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44" s="39">
+        <v>1</v>
+      </c>
+      <c r="G44" s="35">
         <v>12000</v>
       </c>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="39">
+      <c r="A45" s="32">
         <v>35</v>
       </c>
-      <c r="B45" s="48" t="s">
+      <c r="B45" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="47" t="s">
+      <c r="C45" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="53" t="s">
+      <c r="D45" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="41">
-        <v>1</v>
-      </c>
-      <c r="G45" s="42">
+      <c r="E45" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="34">
+        <v>1</v>
+      </c>
+      <c r="G45" s="35">
         <v>6000</v>
       </c>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="39">
+      <c r="A46" s="32">
         <v>36</v>
       </c>
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="47" t="s">
+      <c r="C46" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="40" t="s">
+      <c r="D46" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E46" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="46">
-        <v>1</v>
-      </c>
-      <c r="G46" s="42">
+      <c r="E46" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="39">
+        <v>1</v>
+      </c>
+      <c r="G46" s="35">
         <v>32000</v>
       </c>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="39">
+      <c r="A47" s="32">
         <v>37</v>
       </c>
-      <c r="B47" s="48" t="s">
+      <c r="B47" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="40" t="s">
+      <c r="D47" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E47" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F47" s="41">
-        <v>1</v>
-      </c>
-      <c r="G47" s="42">
+      <c r="E47" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47" s="34">
+        <v>1</v>
+      </c>
+      <c r="G47" s="35">
         <v>32000</v>
       </c>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="39">
+      <c r="A48" s="32">
         <v>38</v>
       </c>
-      <c r="B48" s="47" t="s">
+      <c r="B48" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D48" s="40" t="s">
+      <c r="D48" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F48" s="46">
-        <v>1</v>
-      </c>
-      <c r="G48" s="42">
+      <c r="E48" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="39">
+        <v>1</v>
+      </c>
+      <c r="G48" s="35">
         <v>32000</v>
       </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="39">
+      <c r="A49" s="32">
         <v>39</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="D49" s="40" t="s">
+      <c r="D49" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F49" s="41">
-        <v>1</v>
-      </c>
-      <c r="G49" s="42">
+      <c r="E49" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49" s="34">
+        <v>1</v>
+      </c>
+      <c r="G49" s="35">
         <v>32000</v>
       </c>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="39">
+      <c r="A50" s="32">
         <v>40</v>
       </c>
-      <c r="B50" s="47" t="s">
+      <c r="B50" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="D50" s="47" t="s">
+      <c r="D50" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="E50" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F50" s="46">
-        <v>1</v>
-      </c>
-      <c r="G50" s="42">
+      <c r="E50" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F50" s="39">
+        <v>1</v>
+      </c>
+      <c r="G50" s="35">
         <v>12000</v>
       </c>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="39">
+      <c r="A51" s="32">
         <v>41</v>
       </c>
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C51" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="D51" s="47" t="s">
+      <c r="D51" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F51" s="41">
-        <v>1</v>
-      </c>
-      <c r="G51" s="42">
+      <c r="E51" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F51" s="34">
+        <v>1</v>
+      </c>
+      <c r="G51" s="35">
         <v>12000</v>
       </c>
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="39">
+      <c r="A52" s="32">
         <v>42</v>
       </c>
-      <c r="B52" s="48" t="s">
+      <c r="B52" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="48" t="s">
+      <c r="C52" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="D52" s="40" t="s">
+      <c r="D52" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E52" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F52" s="46">
-        <v>1</v>
-      </c>
-      <c r="G52" s="42">
+      <c r="E52" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F52" s="39">
+        <v>1</v>
+      </c>
+      <c r="G52" s="35">
         <v>6000</v>
       </c>
       <c r="H52" s="9"/>
     </row>
     <row r="53" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="39">
+      <c r="A53" s="32">
         <v>43</v>
       </c>
-      <c r="B53" s="48" t="s">
+      <c r="B53" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="48" t="s">
+      <c r="C53" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="D53" s="40" t="s">
+      <c r="D53" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" s="41">
-        <v>1</v>
-      </c>
-      <c r="G53" s="42">
+      <c r="E53" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F53" s="34">
+        <v>1</v>
+      </c>
+      <c r="G53" s="35">
         <v>6000</v>
       </c>
       <c r="H53" s="9"/>
     </row>
     <row r="54" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="39">
+      <c r="A54" s="32">
         <v>44</v>
       </c>
-      <c r="B54" s="48" t="s">
+      <c r="B54" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="D54" s="40" t="s">
+      <c r="D54" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E54" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F54" s="46">
-        <v>1</v>
-      </c>
-      <c r="G54" s="42">
+      <c r="E54" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F54" s="39">
+        <v>1</v>
+      </c>
+      <c r="G54" s="35">
         <v>6000</v>
       </c>
       <c r="H54" s="9"/>
     </row>
     <row r="55" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="39">
+      <c r="A55" s="32">
         <v>45</v>
       </c>
-      <c r="B55" s="49" t="s">
+      <c r="B55" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="48" t="s">
+      <c r="C55" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="D55" s="40" t="s">
+      <c r="D55" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E55" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F55" s="41">
-        <v>1</v>
-      </c>
-      <c r="G55" s="42">
+      <c r="E55" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F55" s="34">
+        <v>1</v>
+      </c>
+      <c r="G55" s="35">
         <v>6000</v>
       </c>
       <c r="H55" s="9"/>
     </row>
     <row r="56" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="39">
+      <c r="A56" s="32">
         <v>46</v>
       </c>
-      <c r="B56" s="49" t="s">
+      <c r="B56" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="C56" s="49" t="s">
+      <c r="C56" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="49" t="s">
+      <c r="D56" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="E56" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F56" s="46">
-        <v>1</v>
-      </c>
-      <c r="G56" s="42">
+      <c r="E56" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56" s="39">
+        <v>1</v>
+      </c>
+      <c r="G56" s="35">
         <v>6000</v>
       </c>
       <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="39">
+      <c r="A57" s="32">
         <v>47</v>
       </c>
-      <c r="B57" s="49" t="s">
+      <c r="B57" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C57" s="48" t="s">
+      <c r="C57" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D57" s="40" t="s">
+      <c r="D57" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="E57" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F57" s="41">
-        <v>1</v>
-      </c>
-      <c r="G57" s="42">
+      <c r="E57" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="34">
+        <v>1</v>
+      </c>
+      <c r="G57" s="35">
         <v>32000</v>
       </c>
       <c r="H57" s="9"/>
     </row>
     <row r="58" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="39">
+      <c r="A58" s="32">
         <v>48</v>
       </c>
-      <c r="B58" s="48" t="s">
+      <c r="B58" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="48" t="s">
+      <c r="C58" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D58" s="40" t="s">
+      <c r="D58" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E58" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F58" s="46">
-        <v>1</v>
-      </c>
-      <c r="G58" s="42">
+      <c r="E58" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F58" s="39">
+        <v>1</v>
+      </c>
+      <c r="G58" s="35">
         <v>32000</v>
       </c>
       <c r="H58" s="9"/>
     </row>
     <row r="59" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="39">
+      <c r="A59" s="32">
         <v>49</v>
       </c>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="48" t="s">
+      <c r="C59" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="40" t="s">
+      <c r="D59" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E59" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F59" s="41">
-        <v>1</v>
-      </c>
-      <c r="G59" s="42">
+      <c r="E59" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" s="34">
+        <v>1</v>
+      </c>
+      <c r="G59" s="35">
         <v>32000</v>
       </c>
       <c r="H59" s="9"/>
     </row>
     <row r="60" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="39">
+      <c r="A60" s="32">
         <v>50</v>
       </c>
-      <c r="B60" s="51" t="s">
+      <c r="B60" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="51" t="s">
+      <c r="C60" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="D60" s="50" t="s">
+      <c r="D60" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E60" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F60" s="46">
-        <v>1</v>
-      </c>
-      <c r="G60" s="42">
+      <c r="E60" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F60" s="39">
+        <v>1</v>
+      </c>
+      <c r="G60" s="35">
         <v>38000</v>
       </c>
       <c r="H60" s="9"/>
     </row>
     <row r="61" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="39">
+      <c r="A61" s="32">
         <v>51</v>
       </c>
-      <c r="B61" s="51" t="s">
+      <c r="B61" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C61" s="51" t="s">
+      <c r="C61" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="D61" s="50" t="s">
+      <c r="D61" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E61" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F61" s="41">
-        <v>1</v>
-      </c>
-      <c r="G61" s="42">
+      <c r="E61" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F61" s="34">
+        <v>1</v>
+      </c>
+      <c r="G61" s="35">
         <v>38000</v>
       </c>
       <c r="H61" s="9"/>
     </row>
     <row r="62" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="39">
+      <c r="A62" s="32">
         <v>52</v>
       </c>
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="51" t="s">
+      <c r="C62" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="D62" s="40" t="s">
+      <c r="D62" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F62" s="47">
-        <v>1</v>
-      </c>
-      <c r="G62" s="42">
+      <c r="E62" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F62" s="40">
+        <v>1</v>
+      </c>
+      <c r="G62" s="35">
         <v>25000</v>
       </c>
       <c r="H62" s="9"/>
     </row>
     <row r="63" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="39">
+      <c r="A63" s="32">
         <v>53</v>
       </c>
-      <c r="B63" s="47" t="s">
+      <c r="B63" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C63" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="D63" s="40" t="s">
+      <c r="D63" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F63" s="47">
-        <v>1</v>
-      </c>
-      <c r="G63" s="42">
+      <c r="E63" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F63" s="40">
+        <v>1</v>
+      </c>
+      <c r="G63" s="35">
         <v>63000</v>
       </c>
       <c r="H63" s="9"/>
     </row>
     <row r="64" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="39">
+      <c r="A64" s="32">
         <v>54</v>
       </c>
-      <c r="B64" s="48" t="s">
+      <c r="B64" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="48" t="s">
+      <c r="C64" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D64" s="40" t="s">
+      <c r="D64" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="E64" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F64" s="47">
-        <v>1</v>
-      </c>
-      <c r="G64" s="42">
+      <c r="E64" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F64" s="40">
+        <v>1</v>
+      </c>
+      <c r="G64" s="35">
         <v>44000</v>
       </c>
       <c r="H64" s="9"/>
     </row>
     <row r="65" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="39">
+      <c r="A65" s="32">
         <v>55</v>
       </c>
-      <c r="B65" s="54" t="s">
+      <c r="B65" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="48" t="s">
+      <c r="C65" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D65" s="40" t="s">
+      <c r="D65" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="E65" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F65" s="47">
-        <v>1</v>
-      </c>
-      <c r="G65" s="42">
+      <c r="E65" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F65" s="40">
+        <v>1</v>
+      </c>
+      <c r="G65" s="35">
         <v>44000</v>
       </c>
       <c r="H65" s="9"/>
     </row>
     <row r="66" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="39">
+      <c r="A66" s="32">
         <v>56</v>
       </c>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C66" s="48" t="s">
+      <c r="C66" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D66" s="40" t="s">
+      <c r="D66" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="E66" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F66" s="47">
-        <v>1</v>
-      </c>
-      <c r="G66" s="42">
+      <c r="E66" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F66" s="40">
+        <v>1</v>
+      </c>
+      <c r="G66" s="35">
         <v>38000</v>
       </c>
       <c r="H66" s="9"/>
     </row>
     <row r="67" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="39">
+      <c r="A67" s="32">
         <v>57</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="48" t="s">
+      <c r="C67" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="D67" s="40" t="s">
+      <c r="D67" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E67" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F67" s="47">
-        <v>1</v>
-      </c>
-      <c r="G67" s="42">
+      <c r="E67" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F67" s="40">
+        <v>1</v>
+      </c>
+      <c r="G67" s="35">
         <v>44000</v>
       </c>
       <c r="H67" s="9"/>
     </row>
     <row r="68" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="39">
+      <c r="A68" s="32">
         <v>58</v>
       </c>
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="47" t="s">
+      <c r="C68" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="D68" s="40" t="s">
+      <c r="D68" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E68" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F68" s="47">
-        <v>1</v>
-      </c>
-      <c r="G68" s="42">
+      <c r="E68" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F68" s="40">
+        <v>1</v>
+      </c>
+      <c r="G68" s="35">
         <v>25000</v>
       </c>
       <c r="H68" s="9"/>
     </row>
     <row r="69" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="39">
+      <c r="A69" s="32">
         <v>59</v>
       </c>
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="47" t="s">
+      <c r="C69" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D69" s="40" t="s">
+      <c r="D69" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E69" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F69" s="47">
-        <v>1</v>
-      </c>
-      <c r="G69" s="42">
+      <c r="E69" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F69" s="40">
+        <v>1</v>
+      </c>
+      <c r="G69" s="35">
         <v>12000</v>
       </c>
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="39">
+      <c r="A70" s="32">
         <v>60</v>
       </c>
-      <c r="B70" s="47" t="s">
+      <c r="B70" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="47" t="s">
+      <c r="C70" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D70" s="40" t="s">
+      <c r="D70" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E70" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F70" s="47">
-        <v>1</v>
-      </c>
-      <c r="G70" s="42">
+      <c r="E70" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F70" s="40">
+        <v>1</v>
+      </c>
+      <c r="G70" s="35">
         <v>12000</v>
       </c>
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="39">
+      <c r="A71" s="32">
         <v>61</v>
       </c>
-      <c r="B71" s="47" t="s">
+      <c r="B71" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C71" s="47" t="s">
+      <c r="C71" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D71" s="40" t="s">
+      <c r="D71" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E71" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F71" s="47">
-        <v>1</v>
-      </c>
-      <c r="G71" s="42">
+      <c r="E71" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F71" s="40">
+        <v>1</v>
+      </c>
+      <c r="G71" s="35">
         <v>12000</v>
       </c>
       <c r="H71" s="9"/>
     </row>
     <row r="72" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="39">
+      <c r="A72" s="32">
         <v>62</v>
       </c>
-      <c r="B72" s="47" t="s">
+      <c r="B72" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="47" t="s">
+      <c r="C72" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D72" s="40" t="s">
+      <c r="D72" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E72" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F72" s="47">
-        <v>1</v>
-      </c>
-      <c r="G72" s="42">
+      <c r="E72" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F72" s="40">
+        <v>1</v>
+      </c>
+      <c r="G72" s="35">
         <v>12000</v>
       </c>
       <c r="H72" s="9"/>
     </row>
     <row r="73" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="39">
+      <c r="A73" s="32">
         <v>63</v>
       </c>
-      <c r="B73" s="48" t="s">
+      <c r="B73" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="47" t="s">
+      <c r="C73" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D73" s="40" t="s">
+      <c r="D73" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E73" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F73" s="47">
-        <v>1</v>
-      </c>
-      <c r="G73" s="42">
+      <c r="E73" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F73" s="40">
+        <v>1</v>
+      </c>
+      <c r="G73" s="35">
         <v>12000</v>
       </c>
       <c r="H73" s="9"/>
     </row>
     <row r="74" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="39">
+      <c r="A74" s="32">
         <v>64</v>
       </c>
-      <c r="B74" s="52" t="s">
+      <c r="B74" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C74" s="47" t="s">
+      <c r="C74" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D74" s="39" t="s">
+      <c r="D74" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="E74" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F74" s="47">
-        <v>1</v>
-      </c>
-      <c r="G74" s="42">
+      <c r="E74" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F74" s="40">
+        <v>1</v>
+      </c>
+      <c r="G74" s="35">
         <v>25000</v>
       </c>
       <c r="H74" s="9"/>
     </row>
     <row r="75" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="39">
+      <c r="A75" s="32">
         <v>65</v>
       </c>
-      <c r="B75" s="55" t="s">
+      <c r="B75" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="C75" s="47" t="s">
+      <c r="C75" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D75" s="40" t="s">
+      <c r="D75" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E75" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F75" s="47">
-        <v>1</v>
-      </c>
-      <c r="G75" s="42">
+      <c r="E75" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F75" s="40">
+        <v>1</v>
+      </c>
+      <c r="G75" s="35">
         <v>25000</v>
       </c>
       <c r="H75" s="9"/>
     </row>
     <row r="76" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="39">
+      <c r="A76" s="32">
         <v>66</v>
       </c>
-      <c r="B76" s="55" t="s">
+      <c r="B76" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="C76" s="47" t="s">
+      <c r="C76" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D76" s="40" t="s">
+      <c r="D76" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="E76" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F76" s="47">
-        <v>1</v>
-      </c>
-      <c r="G76" s="42">
+      <c r="E76" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F76" s="40">
+        <v>1</v>
+      </c>
+      <c r="G76" s="35">
         <v>25000</v>
       </c>
       <c r="H76" s="9"/>
     </row>
     <row r="77" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="39">
+      <c r="A77" s="32">
         <v>67</v>
       </c>
-      <c r="B77" s="55" t="s">
+      <c r="B77" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="47" t="s">
+      <c r="C77" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="40" t="s">
+      <c r="D77" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F77" s="47">
-        <v>1</v>
-      </c>
-      <c r="G77" s="42"/>
+      <c r="E77" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F77" s="40">
+        <v>1</v>
+      </c>
+      <c r="G77" s="35"/>
       <c r="H77" s="9"/>
     </row>
     <row r="78" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="39">
+      <c r="A78" s="32">
         <v>68</v>
       </c>
-      <c r="B78" s="47" t="s">
+      <c r="B78" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C78" s="47" t="s">
+      <c r="C78" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="D78" s="56" t="s">
+      <c r="D78" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="E78" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F78" s="57">
-        <v>1</v>
-      </c>
-      <c r="G78" s="42">
+      <c r="E78" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F78" s="73">
+        <v>1</v>
+      </c>
+      <c r="G78" s="35">
         <v>8000</v>
       </c>
       <c r="H78" s="9"/>
     </row>
     <row r="79" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="39">
+      <c r="A79" s="32">
         <v>69</v>
       </c>
-      <c r="B79" s="51" t="s">
+      <c r="B79" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="C79" s="58" t="s">
+      <c r="C79" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="59"/>
-      <c r="E79" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F79" s="60"/>
-      <c r="G79" s="42">
+      <c r="D79" s="72"/>
+      <c r="E79" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F79" s="74"/>
+      <c r="G79" s="35">
         <v>8000</v>
       </c>
       <c r="H79" s="9"/>
     </row>
     <row r="80" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="39">
+      <c r="A80" s="32">
         <v>70</v>
       </c>
-      <c r="B80" s="48" t="s">
+      <c r="B80" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C80" s="48" t="s">
+      <c r="C80" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D80" s="40" t="s">
+      <c r="D80" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E80" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F80" s="47">
-        <v>1</v>
-      </c>
-      <c r="G80" s="42">
+      <c r="E80" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F80" s="40">
+        <v>1</v>
+      </c>
+      <c r="G80" s="35">
         <v>6000</v>
       </c>
       <c r="H80" s="9"/>
     </row>
     <row r="81" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="39">
+      <c r="A81" s="32">
         <v>71</v>
       </c>
-      <c r="B81" s="54" t="s">
+      <c r="B81" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C81" s="54" t="s">
+      <c r="C81" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="D81" s="40" t="s">
+      <c r="D81" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="E81" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F81" s="47">
-        <v>1</v>
-      </c>
-      <c r="G81" s="42">
+      <c r="E81" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F81" s="40">
+        <v>1</v>
+      </c>
+      <c r="G81" s="35">
         <v>6000</v>
       </c>
       <c r="H81" s="9"/>
     </row>
     <row r="82" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="39">
+      <c r="A82" s="32">
         <v>72</v>
       </c>
-      <c r="B82" s="61" t="s">
+      <c r="B82" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C82" s="61" t="s">
+      <c r="C82" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="D82" s="40" t="s">
+      <c r="D82" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E82" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F82" s="47">
-        <v>1</v>
-      </c>
-      <c r="G82" s="42">
+      <c r="E82" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F82" s="40">
+        <v>1</v>
+      </c>
+      <c r="G82" s="35">
         <v>100000</v>
       </c>
       <c r="H82" s="9"/>
     </row>
     <row r="83" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="39">
+      <c r="A83" s="32">
         <v>73</v>
       </c>
-      <c r="B83" s="49" t="s">
+      <c r="B83" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C83" s="49" t="s">
+      <c r="C83" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="D83" s="40" t="s">
+      <c r="D83" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E83" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F83" s="47">
-        <v>1</v>
-      </c>
-      <c r="G83" s="42">
+      <c r="E83" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F83" s="40">
+        <v>1</v>
+      </c>
+      <c r="G83" s="35">
         <v>9000</v>
       </c>
       <c r="H83" s="9"/>
     </row>
     <row r="84" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="39">
+      <c r="A84" s="32">
         <v>74</v>
       </c>
-      <c r="B84" s="48" t="s">
+      <c r="B84" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C84" s="49" t="s">
+      <c r="C84" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="D84" s="40" t="s">
+      <c r="D84" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E84" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F84" s="47">
-        <v>1</v>
-      </c>
-      <c r="G84" s="42">
+      <c r="E84" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F84" s="40">
+        <v>1</v>
+      </c>
+      <c r="G84" s="35">
         <v>18000</v>
       </c>
       <c r="H84" s="9"/>
     </row>
     <row r="85" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="39">
+      <c r="A85" s="32">
         <v>75</v>
       </c>
-      <c r="B85" s="48" t="s">
+      <c r="B85" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="C85" s="48" t="s">
+      <c r="C85" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D85" s="40" t="s">
+      <c r="D85" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E85" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F85" s="47">
-        <v>1</v>
-      </c>
-      <c r="G85" s="62">
+      <c r="E85" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F85" s="40">
+        <v>1</v>
+      </c>
+      <c r="G85" s="51">
         <v>9000</v>
       </c>
       <c r="H85" s="9"/>
     </row>
     <row r="86" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="39">
+      <c r="A86" s="32">
         <v>76</v>
       </c>
-      <c r="B86" s="48" t="s">
+      <c r="B86" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C86" s="48" t="s">
+      <c r="C86" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D86" s="40" t="s">
+      <c r="D86" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E86" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F86" s="47">
-        <v>1</v>
-      </c>
-      <c r="G86" s="62">
+      <c r="E86" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F86" s="40">
+        <v>1</v>
+      </c>
+      <c r="G86" s="51">
         <v>18000</v>
       </c>
       <c r="H86" s="9"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" s="39">
+      <c r="A87" s="32">
         <v>77</v>
       </c>
-      <c r="B87" s="48" t="s">
+      <c r="B87" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C87" s="63"/>
-      <c r="D87" s="39"/>
-      <c r="E87" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F87" s="47">
-        <v>1</v>
-      </c>
-      <c r="G87" s="62"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F87" s="40">
+        <v>1</v>
+      </c>
+      <c r="G87" s="51"/>
       <c r="H87" s="14"/>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="39">
+      <c r="A88" s="32">
         <v>78</v>
       </c>
-      <c r="B88" s="39" t="s">
+      <c r="B88" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="C88" s="39"/>
-      <c r="D88" s="39"/>
-      <c r="E88" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F88" s="39">
-        <v>1</v>
-      </c>
-      <c r="G88" s="64"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F88" s="32">
+        <v>1</v>
+      </c>
+      <c r="G88" s="53"/>
       <c r="H88" s="27"/>
       <c r="I88" s="8"/>
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="39">
+      <c r="A89" s="32">
         <v>79</v>
       </c>
-      <c r="B89" s="47" t="s">
+      <c r="B89" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="C89" s="47"/>
-      <c r="D89" s="47" t="s">
+      <c r="C89" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="D89" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="E89" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="F89" s="47">
-        <v>1</v>
-      </c>
-      <c r="G89" s="65">
+      <c r="E89" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="F89" s="40">
+        <v>1</v>
+      </c>
+      <c r="G89" s="54">
         <v>200000</v>
       </c>
-      <c r="H89" s="66"/>
+      <c r="H89" s="55"/>
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="39">
+      <c r="A90" s="32">
         <v>80</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="C90" s="52"/>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F90" s="52"/>
-      <c r="G90" s="67">
+      <c r="C90" s="84" t="s">
+        <v>193</v>
+      </c>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F90" s="45"/>
+      <c r="G90" s="56">
         <v>230000</v>
       </c>
-      <c r="H90" s="52" t="s">
+      <c r="H90" s="45" t="s">
         <v>189</v>
       </c>
       <c r="I90" s="8"/>
@@ -3655,111 +3689,121 @@
       <c r="K90" s="8"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="39">
+      <c r="A91" s="32">
         <v>81</v>
       </c>
-      <c r="B91" s="39" t="s">
+      <c r="B91" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="C91" s="52"/>
-      <c r="D91" s="52"/>
-      <c r="E91" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F91" s="52"/>
-      <c r="G91" s="67">
+      <c r="C91" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F91" s="45"/>
+      <c r="G91" s="56">
         <v>260000</v>
       </c>
-      <c r="H91" s="52" t="s">
+      <c r="H91" s="45" t="s">
         <v>190</v>
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="39">
+    <row r="92" spans="1:11" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="A92" s="32">
         <v>82</v>
       </c>
-      <c r="B92" s="39" t="s">
+      <c r="B92" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="52"/>
-      <c r="D92" s="52"/>
-      <c r="E92" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F92" s="52"/>
-      <c r="G92" s="67">
+      <c r="C92" s="84" t="s">
+        <v>195</v>
+      </c>
+      <c r="D92" s="45"/>
+      <c r="E92" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F92" s="45"/>
+      <c r="G92" s="56">
         <v>80000</v>
       </c>
-      <c r="H92" s="52" t="s">
+      <c r="H92" s="45" t="s">
         <v>190</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="39">
+    <row r="93" spans="1:11" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="A93" s="32">
         <v>83</v>
       </c>
-      <c r="B93" s="39" t="s">
+      <c r="B93" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F93" s="52"/>
-      <c r="G93" s="67">
+      <c r="C93" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="D93" s="45"/>
+      <c r="E93" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F93" s="45"/>
+      <c r="G93" s="56">
         <v>150000</v>
       </c>
-      <c r="H93" s="52" t="s">
+      <c r="H93" s="45" t="s">
         <v>190</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
     </row>
     <row r="94" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="39">
+      <c r="A94" s="32">
         <v>84</v>
       </c>
-      <c r="B94" s="39" t="s">
+      <c r="B94" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="52"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F94" s="52"/>
-      <c r="G94" s="67">
+      <c r="C94" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="D94" s="45"/>
+      <c r="E94" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F94" s="45"/>
+      <c r="G94" s="56">
         <v>100000</v>
       </c>
-      <c r="H94" s="52" t="s">
+      <c r="H94" s="45" t="s">
         <v>190</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95" s="39">
+      <c r="A95" s="32">
         <v>85</v>
       </c>
-      <c r="B95" s="39" t="s">
+      <c r="B95" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52" t="s">
+      <c r="C95" s="84" t="s">
+        <v>198</v>
+      </c>
+      <c r="D95" s="45"/>
+      <c r="E95" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F95" s="45"/>
+      <c r="G95" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="H95" s="52" t="s">
+      <c r="H95" s="45" t="s">
         <v>190</v>
       </c>
       <c r="I95" s="8"/>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1823504-2F7F-4628-97B7-1525BB6B8FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D172EDA-B673-4EE8-9FD3-6FEE2ADCB1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1230,6 +1230,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1268,9 +1271,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1708,44 +1708,44 @@
       <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="78"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="79"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="80"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="81"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="82"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="83"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
       <c r="E9" s="13"/>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
@@ -3393,13 +3393,13 @@
       <c r="C78" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="D78" s="71" t="s">
+      <c r="D78" s="72" t="s">
         <v>75</v>
       </c>
       <c r="E78" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F78" s="73">
+      <c r="F78" s="74">
         <v>1</v>
       </c>
       <c r="G78" s="35">
@@ -3417,11 +3417,11 @@
       <c r="C79" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="72"/>
+      <c r="D79" s="73"/>
       <c r="E79" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F79" s="74"/>
+      <c r="F79" s="75"/>
       <c r="G79" s="35">
         <v>8000</v>
       </c>
@@ -3670,7 +3670,7 @@
       <c r="B90" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="C90" s="84" t="s">
+      <c r="C90" s="71" t="s">
         <v>193</v>
       </c>
       <c r="D90" s="45"/>
@@ -3695,7 +3695,7 @@
       <c r="B91" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="C91" s="84" t="s">
+      <c r="C91" s="71" t="s">
         <v>194</v>
       </c>
       <c r="D91" s="45"/>
@@ -3720,7 +3720,7 @@
       <c r="B92" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="84" t="s">
+      <c r="C92" s="71" t="s">
         <v>195</v>
       </c>
       <c r="D92" s="45"/>
@@ -3744,7 +3744,7 @@
       <c r="B93" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="71" t="s">
         <v>196</v>
       </c>
       <c r="D93" s="45"/>
@@ -3756,19 +3756,19 @@
         <v>150000</v>
       </c>
       <c r="H93" s="45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
     </row>
-    <row r="94" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="32">
         <v>84</v>
       </c>
       <c r="B94" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="84" t="s">
+      <c r="C94" s="71" t="s">
         <v>197</v>
       </c>
       <c r="D94" s="45"/>
@@ -3792,7 +3792,7 @@
       <c r="B95" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="84" t="s">
+      <c r="C95" s="71" t="s">
         <v>198</v>
       </c>
       <c r="D95" s="45"/>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D172EDA-B673-4EE8-9FD3-6FEE2ADCB1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D9EDA9-DFBE-498F-B3DC-4A5CDC979B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3677,7 +3677,9 @@
       <c r="E90" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F90" s="45"/>
+      <c r="F90" s="40">
+        <v>1</v>
+      </c>
       <c r="G90" s="56">
         <v>230000</v>
       </c>
@@ -3702,7 +3704,9 @@
       <c r="E91" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F91" s="45"/>
+      <c r="F91" s="40">
+        <v>1</v>
+      </c>
       <c r="G91" s="56">
         <v>260000</v>
       </c>
@@ -3727,7 +3731,9 @@
       <c r="E92" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F92" s="45"/>
+      <c r="F92" s="40">
+        <v>1</v>
+      </c>
       <c r="G92" s="56">
         <v>80000</v>
       </c>
@@ -3751,7 +3757,9 @@
       <c r="E93" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F93" s="45"/>
+      <c r="F93" s="40">
+        <v>1</v>
+      </c>
       <c r="G93" s="56">
         <v>150000</v>
       </c>
@@ -3775,7 +3783,9 @@
       <c r="E94" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F94" s="45"/>
+      <c r="F94" s="40">
+        <v>1</v>
+      </c>
       <c r="G94" s="56">
         <v>100000</v>
       </c>
@@ -3799,7 +3809,9 @@
       <c r="E95" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F95" s="45"/>
+      <c r="F95" s="40">
+        <v>1</v>
+      </c>
       <c r="G95" s="45" t="s">
         <v>191</v>
       </c>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D9EDA9-DFBE-498F-B3DC-4A5CDC979B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F5FD00-6917-42D9-AFC6-19BE44FDC6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="203">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -622,6 +622,15 @@
   </si>
   <si>
     <t>Module SIM</t>
+  </si>
+  <si>
+    <t>eSIM</t>
+  </si>
+  <si>
+    <t>Phí dịch vụ hoà mạng</t>
+  </si>
+  <si>
+    <t>Nếu khách hàng không hoà mạng cung cấp Seri cho khách tự hoà mạng</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1049,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1271,6 +1280,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3822,26 +3840,50 @@
       <c r="J95" s="8"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
+      <c r="A96" s="85">
+        <v>86</v>
+      </c>
+      <c r="B96" s="85" t="s">
+        <v>200</v>
+      </c>
+      <c r="C96" s="85" t="s">
+        <v>200</v>
+      </c>
+      <c r="D96" s="85"/>
+      <c r="E96" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="F96" s="85">
+        <v>1</v>
+      </c>
+      <c r="G96" s="86">
+        <v>50000</v>
+      </c>
+      <c r="H96" s="85"/>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
+    <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.3">
+      <c r="A97" s="85">
+        <v>87</v>
+      </c>
+      <c r="B97" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="C97" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" s="85"/>
+      <c r="E97" s="85"/>
+      <c r="F97" s="85">
+        <v>1</v>
+      </c>
+      <c r="G97" s="86">
+        <v>60000</v>
+      </c>
+      <c r="H97" s="87" t="s">
+        <v>202</v>
+      </c>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
     </row>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F5FD00-6917-42D9-AFC6-19BE44FDC6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6899BB30-3741-4FD8-A6C4-9A146DBE3F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="205">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -631,13 +631,19 @@
   </si>
   <si>
     <t>Nếu khách hàng không hoà mạng cung cấp Seri cho khách tự hoà mạng</t>
+  </si>
+  <si>
+    <t>SIM 65M-C</t>
+  </si>
+  <si>
+    <t>VT_Sim65M-C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -775,6 +781,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF081B3A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1049,7 +1061,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1242,6 +1254,15 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1282,14 +1303,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1726,44 +1745,44 @@
       <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="79"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="82"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="81"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="84"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="83"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="86"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
       <c r="E9" s="13"/>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
@@ -3411,13 +3430,13 @@
       <c r="C78" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="D78" s="72" t="s">
+      <c r="D78" s="75" t="s">
         <v>75</v>
       </c>
       <c r="E78" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F78" s="74">
+      <c r="F78" s="77">
         <v>1</v>
       </c>
       <c r="G78" s="35">
@@ -3435,11 +3454,11 @@
       <c r="C79" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="73"/>
+      <c r="D79" s="76"/>
       <c r="E79" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F79" s="75"/>
+      <c r="F79" s="78"/>
       <c r="G79" s="35">
         <v>8000</v>
       </c>
@@ -3840,62 +3859,76 @@
       <c r="J95" s="8"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="85">
+      <c r="A96" s="72">
         <v>86</v>
       </c>
-      <c r="B96" s="85" t="s">
+      <c r="B96" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="C96" s="85" t="s">
+      <c r="C96" s="72" t="s">
         <v>200</v>
       </c>
-      <c r="D96" s="85"/>
-      <c r="E96" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="F96" s="85">
-        <v>1</v>
-      </c>
-      <c r="G96" s="86">
+      <c r="D96" s="72"/>
+      <c r="E96" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="F96" s="72">
+        <v>1</v>
+      </c>
+      <c r="G96" s="73">
         <v>50000</v>
       </c>
-      <c r="H96" s="85"/>
+      <c r="H96" s="72"/>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
     </row>
     <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.3">
-      <c r="A97" s="85">
+      <c r="A97" s="72">
         <v>87</v>
       </c>
-      <c r="B97" s="85" t="s">
+      <c r="B97" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="C97" s="85" t="s">
+      <c r="C97" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="D97" s="85"/>
-      <c r="E97" s="85"/>
-      <c r="F97" s="85">
-        <v>1</v>
-      </c>
-      <c r="G97" s="86">
+      <c r="D97" s="72"/>
+      <c r="E97" s="72"/>
+      <c r="F97" s="72">
+        <v>1</v>
+      </c>
+      <c r="G97" s="73">
         <v>60000</v>
       </c>
-      <c r="H97" s="87" t="s">
+      <c r="H97" s="74" t="s">
         <v>202</v>
       </c>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
+      <c r="A98" s="88">
+        <v>88</v>
+      </c>
+      <c r="B98" s="90" t="s">
+        <v>204</v>
+      </c>
+      <c r="C98" s="88" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" s="88" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="F98" s="88">
+        <v>1</v>
+      </c>
+      <c r="G98" s="89">
+        <v>110000</v>
+      </c>
+      <c r="H98" s="88"/>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
     </row>

--- a/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
+++ b/5. Other/Báo giá linh kiện/Báo giá linh kiện BH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Báo giá linh kiện\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6899BB30-3741-4FD8-A6C4-9A146DBE3F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A64B60-4427-4CA0-B7AB-4E7B79869AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
